--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>104185</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734513.1610765377</v>
+        <v>734513</v>
       </c>
       <c r="R2" t="n">
-        <v>6425954.816859737</v>
+        <v>6425955</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2002-07-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106657</v>
+        <v>106666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106666</v>
+        <v>106678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106678</v>
+        <v>106687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106687</v>
+        <v>106692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106692</v>
+        <v>106720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106720</v>
+        <v>106726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106726</v>
+        <v>106733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106733</v>
+        <v>106737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106737</v>
+        <v>106744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106747</v>
+        <v>106752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105210378</v>
       </c>
       <c r="B2" t="n">
-        <v>106752</v>
+        <v>106760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105210378</v>
+        <v>61023376</v>
       </c>
       <c r="B2" t="n">
-        <v>106760</v>
+        <v>107292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -713,16 +713,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ar, hamnpiren, 700 m SO, Gtl</t>
+          <t>Fleringe, Ar, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734513</v>
+        <v>734531</v>
       </c>
       <c r="R2" t="n">
-        <v>6425955</v>
+        <v>6425972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +755,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-07-24</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-07-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>&gt;100. Mindre bestånd på stranden NO och - xkoord = 1686922, ykoord = 6425384</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,23 +772,240 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkflis.</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Dennis Nyström, Sanne Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69405595</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107292</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>669</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kalkdån</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Galeopsis angustifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ehrh. ex Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fleringe, Nackpallar 400 m V, Hau 1:28 104 m NV, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>734527</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6425967</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fleringe</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-08-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-08-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105210378</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107292</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>669</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kalkdån</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Galeopsis angustifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ehrh. ex Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ar, hamnpiren, 700 m SO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>734513</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6425955</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fleringe</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2002-07-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2002-07-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>&gt;100. Mindre bestånd på stranden NO och - xkoord = 1686922, ykoord = 6425384</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkflis.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>

--- a/artfynd/A 64700-2021 artfynd.xlsx
+++ b/artfynd/A 64700-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61023376</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69405595</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,8 +1025,18 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105210378</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>